--- a/exports/btc-usd_forecast_next7.xlsx
+++ b/exports/btc-usd_forecast_next7.xlsx
@@ -443,71 +443,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94092.49000000001</v>
+        <v>94786.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94109.49000000001</v>
+        <v>94901.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>94704.02</v>
+        <v>95406.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94864.87</v>
+        <v>95776.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95273.05</v>
+        <v>95616.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95748.95</v>
+        <v>95539.67999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95687.57000000001</v>
+        <v>95249.42</v>
       </c>
     </row>
   </sheetData>

--- a/exports/btc-usd_forecast_next7.xlsx
+++ b/exports/btc-usd_forecast_next7.xlsx
@@ -443,71 +443,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94786.66</v>
+        <v>86468.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94901.73</v>
+        <v>86579.46000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95406.66</v>
+        <v>86662.10000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95776.16</v>
+        <v>86184.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95616.09</v>
+        <v>86195.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95539.67999999999</v>
+        <v>86374.49000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95249.42</v>
+        <v>86030.87</v>
       </c>
     </row>
   </sheetData>

--- a/exports/btc-usd_forecast_next7.xlsx
+++ b/exports/btc-usd_forecast_next7.xlsx
@@ -443,71 +443,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86468.27</v>
+        <v>85197.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86579.46000000001</v>
+        <v>85240.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86662.10000000001</v>
+        <v>84764.75999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86184.2</v>
+        <v>84676.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86195.17</v>
+        <v>84877.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86374.49000000001</v>
+        <v>84666.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86030.87</v>
+        <v>84173.85000000001</v>
       </c>
     </row>
   </sheetData>
